--- a/data/trans_bre/P45C_R1-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R1-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,41</t>
+          <t>-1,99; 1,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,5</t>
+          <t>-2,69; 1,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,23</t>
+          <t>-0,14; 3,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,06</t>
+          <t>-1,8; 1,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-82,78; 216,0</t>
+          <t>-85,11; 262,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,52; 201,29</t>
+          <t>-87,69; 191,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-77,67; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-80,41; 209,52</t>
+          <t>-82,5; 184,71</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,22</t>
+          <t>-0,91; 2,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,73</t>
+          <t>-0,51; 3,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,98</t>
+          <t>-1,07; 3,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 3,17</t>
+          <t>-1,38; 3,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,93; 889,5</t>
+          <t>-78,17; 754,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,72; 635,96</t>
+          <t>-36,81; 680,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,41; 686,87</t>
+          <t>-59,8; 731,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,63; 583,91</t>
+          <t>-72,74; 631,87</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,44</t>
+          <t>-2,18; 4,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,86</t>
+          <t>-0,97; 3,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,0</t>
+          <t>-1,19; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,83</t>
+          <t>-2,25; 2,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,92; 206,94</t>
+          <t>-63,3; 203,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,17; 315,03</t>
+          <t>-64,87; 397,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-85,28; 336,22</t>
+          <t>-83,74; 357,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,1</t>
+          <t>-0,64; 2,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,45</t>
+          <t>-0,73; 1,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,85</t>
+          <t>-0,78; 0,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,59</t>
+          <t>-1,59; 0,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 182,58</t>
+          <t>-34,89; 178,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,4; 210,53</t>
+          <t>-56,88; 229,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,47; 224,87</t>
+          <t>-73,28; 207,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,82; 65,22</t>
+          <t>-74,29; 81,45</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,87</t>
+          <t>-1,4; 1,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,96</t>
+          <t>-1,74; 0,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,0</t>
+          <t>-1,38; 0,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,44</t>
+          <t>-2,37; 1,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-64,99; 351,58</t>
+          <t>-66,71; 311,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 138,38</t>
+          <t>-73,82; 130,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 200,36</t>
+          <t>-77,57; 192,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,65; 129,23</t>
+          <t>-63,54; 104,92</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,18</t>
+          <t>-2,09; 1,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,84</t>
+          <t>-0,75; 1,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,65</t>
+          <t>-3,98; 0,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 0,73</t>
+          <t>-6,68; 0,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,01; 433,03</t>
+          <t>-72,51; 388,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,13; —</t>
+          <t>-53,49; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-83,92; 127,03</t>
+          <t>-86,71; 77,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,71</t>
+          <t>-0,7; 0,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,86</t>
+          <t>-0,29; 0,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,72</t>
+          <t>-0,34; 0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,44</t>
+          <t>-0,94; 0,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 58,18</t>
+          <t>-34,33; 46,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 82,83</t>
+          <t>-19,57; 83,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-26,66; 104,46</t>
+          <t>-28,1; 100,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-45,69; 37,19</t>
+          <t>-45,07; 36,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P45C_R1-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R1-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-20,35%</t>
+          <t>-39,28%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,61</t>
+          <t>-1,86; 1,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,14</t>
+          <t>-2,76; 1,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,04</t>
+          <t>-0,22; 3,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,06</t>
+          <t>-2,17; 0,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-85,11; 262,09</t>
+          <t>-83,88; 310,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,69; 191,33</t>
+          <t>-88,06; 176,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-63,55; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-82,5; 184,71</t>
+          <t>-83,18; 141,77</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,36</t>
+          <t>-1,14; 2,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,83</t>
+          <t>-0,42; 3,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,06</t>
+          <t>-1,22; 2,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,22</t>
+          <t>-0,98; 3,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,17; 754,25</t>
+          <t>-80,77; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 680,91</t>
+          <t>-44,98; 781,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,8; 731,98</t>
+          <t>-68,33; 653,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,74; 631,87</t>
+          <t>-59,6; 757,12</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-22,73%</t>
+          <t>-55,23%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,28</t>
+          <t>-2,14; 4,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,09</t>
+          <t>-1,07; 2,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,0</t>
+          <t>-1,34; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,48</t>
+          <t>-3,68; 0,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 203,99</t>
+          <t>-60,43; 222,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 397,19</t>
+          <t>-68,58; 348,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-83,74; 357,09</t>
+          <t>-92,09; 61,22</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-25,51%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,06</t>
+          <t>-0,58; 2,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,54</t>
+          <t>-0,65; 1,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,75</t>
+          <t>-0,72; 0,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,73</t>
+          <t>-0,97; 1,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 178,28</t>
+          <t>-31,83; 199,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,88; 229,74</t>
+          <t>-52,46; 200,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,28; 207,49</t>
+          <t>-71,87; 194,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,29; 81,45</t>
+          <t>-51,94; 148,53</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-9,78%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,94</t>
+          <t>-1,49; 1,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,84</t>
+          <t>-1,85; 0,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,98</t>
+          <t>-1,3; 0,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,23</t>
+          <t>-1,55; 1,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-66,71; 311,77</t>
+          <t>-72,12; 320,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-73,82; 130,0</t>
+          <t>-73,92; 109,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-77,57; 192,53</t>
+          <t>-76,91; 253,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-63,54; 104,92</t>
+          <t>-50,8; 195,99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-56,58%</t>
+          <t>-57,77%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,19</t>
+          <t>-2,22; 1,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,93</t>
+          <t>-0,6; 1,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,47</t>
+          <t>-3,89; 0,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 0,72</t>
+          <t>-5,65; 0,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,51; 388,61</t>
+          <t>-77,1; 349,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,49; —</t>
+          <t>-55,43; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-86,71; 77,57</t>
+          <t>-84,58; 136,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-13,38%</t>
+          <t>-14,09%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,63</t>
+          <t>-0,68; 0,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,83</t>
+          <t>-0,27; 0,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,71</t>
+          <t>-0,27; 0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,43</t>
+          <t>-0,87; 0,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 46,87</t>
+          <t>-34,07; 44,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 83,27</t>
+          <t>-18,63; 84,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 100,44</t>
+          <t>-23,97; 111,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-45,07; 36,49</t>
+          <t>-41,66; 25,46</t>
         </is>
       </c>
     </row>
